--- a/Divisions/Simulations.xlsx
+++ b/Divisions/Simulations.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="186">
   <si>
     <t>Team</t>
   </si>
@@ -136,493 +136,445 @@
     <t>29</t>
   </si>
   <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Inter Miami</t>
   </si>
   <si>
-    <t>LA Galaxy</t>
+    <t>LAFC</t>
   </si>
   <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
-    <t>LAFC</t>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>NY Red Bulls</t>
+  </si>
+  <si>
+    <t>Minnesota Utd</t>
+  </si>
+  <si>
+    <t>NYCFC</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>Vancouver Wcaps</t>
+  </si>
+  <si>
+    <t>Atlanta Utd</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>CF Montreal</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>D.C. United</t>
+  </si>
+  <si>
+    <t>St. Louis</t>
+  </si>
+  <si>
+    <t>Toronto FC</t>
+  </si>
+  <si>
+    <t>NE Revolution</t>
+  </si>
+  <si>
+    <t>Sporting KC</t>
+  </si>
+  <si>
+    <t>SJ Earthquakes</t>
+  </si>
+  <si>
+    <t>Crew</t>
+  </si>
+  <si>
+    <t>Dynamo FC</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Nashville</t>
+  </si>
+  <si>
+    <t>Philadelphia</t>
+  </si>
+  <si>
+    <t>Rapids</t>
   </si>
   <si>
     <t>RSL</t>
   </si>
   <si>
-    <t>Crew</t>
-  </si>
-  <si>
-    <t>NY Red Bulls</t>
-  </si>
-  <si>
-    <t>Rapids</t>
-  </si>
-  <si>
-    <t>NYCFC</t>
-  </si>
-  <si>
-    <t>Vancouver Wcaps</t>
-  </si>
-  <si>
-    <t>Charlotte</t>
-  </si>
-  <si>
-    <t>Dynamo FC</t>
-  </si>
-  <si>
     <t>Seattle</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
-    <t>Orlando City</t>
-  </si>
-  <si>
-    <t>Minnesota Utd</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>Toronto FC</t>
-  </si>
-  <si>
-    <t>Atlanta Utd</t>
-  </si>
-  <si>
-    <t>CF Montreal</t>
-  </si>
-  <si>
-    <t>Philadelphia</t>
-  </si>
-  <si>
-    <t>D.C. United</t>
-  </si>
-  <si>
-    <t>Nashville</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Sporting KC</t>
-  </si>
-  <si>
-    <t>NE Revolution</t>
-  </si>
-  <si>
-    <t>St. Louis</t>
-  </si>
-  <si>
-    <t>SJ Earthquakes</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>-4</t>
+  </si>
+  <si>
+    <t>-3</t>
+  </si>
+  <si>
+    <t>-17</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>mls_teams</t>
+  </si>
+  <si>
+    <t>mls_games_played_sim</t>
+  </si>
+  <si>
+    <t>mls_total_wins_sim</t>
+  </si>
+  <si>
+    <t>mls_total_draws_sim</t>
+  </si>
+  <si>
+    <t>mls_total_loss_sim</t>
+  </si>
+  <si>
+    <t>mls_PTS_sim</t>
+  </si>
+  <si>
+    <t>34</t>
   </si>
   <si>
     <t>56</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>110</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Team_f</t>
+  </si>
+  <si>
+    <t>P_f</t>
+  </si>
+  <si>
+    <t>W_f</t>
+  </si>
+  <si>
+    <t>D_f</t>
+  </si>
+  <si>
+    <t>L_f</t>
+  </si>
+  <si>
+    <t>PTS_f</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>61</t>
+    <t>157</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>arg_GD</t>
+  </si>
+  <si>
+    <t>arg_PTS</t>
+  </si>
+  <si>
+    <t>arg_rank</t>
+  </si>
+  <si>
+    <t>Velez Sarsfield</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
+    <t>Huracan</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Atletico Tucuman</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Union</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Lanus</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Defensa Justicia</t>
+  </si>
+  <si>
+    <t>Gimnasia–LP</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Central Cordoba</t>
+  </si>
+  <si>
+    <t>Arg Juniors</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Newells OB</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>-2</t>
   </si>
   <si>
     <t>-1</t>
   </si>
   <si>
+    <t>-7</t>
+  </si>
+  <si>
     <t>-9</t>
   </si>
   <si>
-    <t>-13</t>
-  </si>
-  <si>
-    <t>-15</t>
-  </si>
-  <si>
-    <t>-12</t>
-  </si>
-  <si>
-    <t>-11</t>
-  </si>
-  <si>
-    <t>-24</t>
-  </si>
-  <si>
-    <t>-14</t>
-  </si>
-  <si>
-    <t>-30</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>mls_teams</t>
-  </si>
-  <si>
-    <t>mls_games_played_sim</t>
-  </si>
-  <si>
-    <t>mls_total_wins_sim</t>
-  </si>
-  <si>
-    <t>mls_total_draws_sim</t>
-  </si>
-  <si>
-    <t>mls_total_loss_sim</t>
-  </si>
-  <si>
-    <t>mls_PTS_sim</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>Team_f</t>
-  </si>
-  <si>
-    <t>P_f</t>
-  </si>
-  <si>
-    <t>W_f</t>
-  </si>
-  <si>
-    <t>D_f</t>
-  </si>
-  <si>
-    <t>L_f</t>
-  </si>
-  <si>
-    <t>PTS_f</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>85</t>
+    <t>arg_teams</t>
+  </si>
+  <si>
+    <t>arg_games_played_sim</t>
+  </si>
+  <si>
+    <t>arg_total_wins_sim</t>
+  </si>
+  <si>
+    <t>arg_total_draws_sim</t>
+  </si>
+  <si>
+    <t>arg_total_loss_sim</t>
+  </si>
+  <si>
+    <t>arg_PTS_sim</t>
   </si>
   <si>
     <t>81</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>arg_GD</t>
-  </si>
-  <si>
-    <t>arg_PTS</t>
-  </si>
-  <si>
-    <t>arg_rank</t>
-  </si>
-  <si>
-    <t>Huracan</t>
-  </si>
-  <si>
-    <t>Union</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Talleres</t>
-  </si>
-  <si>
-    <t>Velez Sarsfield</t>
-  </si>
-  <si>
-    <t>Atletico Tucuman</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Deportivo Riestra</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Lanus</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Arg Juniors</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Gimnasia–LP</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Newells OB</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Defensa Justicia</t>
-  </si>
-  <si>
-    <t>Central Cordoba</t>
-  </si>
-  <si>
-    <t>-4</t>
-  </si>
-  <si>
-    <t>-5</t>
-  </si>
-  <si>
-    <t>-3</t>
-  </si>
-  <si>
-    <t>-7</t>
-  </si>
-  <si>
-    <t>-2</t>
-  </si>
-  <si>
-    <t>-8</t>
-  </si>
-  <si>
-    <t>arg_teams</t>
-  </si>
-  <si>
-    <t>arg_games_played_sim</t>
-  </si>
-  <si>
-    <t>arg_total_wins_sim</t>
-  </si>
-  <si>
-    <t>arg_total_draws_sim</t>
-  </si>
-  <si>
-    <t>arg_total_loss_sim</t>
-  </si>
-  <si>
-    <t>arg_PTS_sim</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>69</t>
   </si>
 </sst>
 </file>
@@ -711,28 +663,28 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K2" t="n">
         <v>1.0</v>
@@ -746,28 +698,28 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K3" t="n">
         <v>2.0</v>
@@ -781,28 +733,28 @@
         <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="K4" t="n">
         <v>3.0</v>
@@ -816,28 +768,28 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="K5" t="n">
         <v>4.0</v>
@@ -851,28 +803,28 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
         <v>5.0</v>
@@ -889,25 +841,25 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>73</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" t="s">
-        <v>76</v>
       </c>
       <c r="K7" t="n">
         <v>6.0</v>
@@ -921,28 +873,28 @@
         <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
         <v>7.0</v>
@@ -956,28 +908,28 @@
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="J9" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
         <v>8.0</v>
@@ -991,28 +943,28 @@
         <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K10" t="n">
         <v>9.0</v>
@@ -1026,28 +978,28 @@
         <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K11" t="n">
         <v>10.0</v>
@@ -1061,28 +1013,28 @@
         <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" t="s">
         <v>77</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" t="s">
-        <v>88</v>
       </c>
       <c r="K12" t="n">
         <v>11.0</v>
@@ -1099,25 +1051,25 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
         <v>77</v>
-      </c>
-      <c r="I13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" t="s">
-        <v>88</v>
       </c>
       <c r="K13" t="n">
         <v>12.0</v>
@@ -1131,28 +1083,28 @@
         <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K14" t="n">
         <v>13.0</v>
@@ -1166,28 +1118,28 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="K15" t="n">
         <v>14.0</v>
@@ -1201,28 +1153,28 @@
         <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K16" t="n">
         <v>15.0</v>
@@ -1236,28 +1188,28 @@
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
         <v>16.0</v>
@@ -1271,28 +1223,28 @@
         <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s">
         <v>16</v>
       </c>
-      <c r="F18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" t="s">
-        <v>88</v>
-      </c>
-      <c r="I18" t="s">
-        <v>94</v>
-      </c>
       <c r="J18" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K18" t="n">
         <v>17.0</v>
@@ -1306,28 +1258,28 @@
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K19" t="n">
         <v>18.0</v>
@@ -1341,28 +1293,28 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
         <v>19.0</v>
@@ -1376,28 +1328,28 @@
         <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="J21" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
         <v>20.0</v>
@@ -1411,28 +1363,28 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
         <v>21.0</v>
@@ -1446,28 +1398,28 @@
         <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
         <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J23" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="K23" t="n">
         <v>22.0</v>
@@ -1481,28 +1433,28 @@
         <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="J24" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="K24" t="n">
         <v>23.0</v>
@@ -1516,28 +1468,28 @@
         <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="K25" t="n">
         <v>24.0</v>
@@ -1551,28 +1503,28 @@
         <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="K26" t="n">
         <v>25.0</v>
@@ -1586,28 +1538,28 @@
         <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="K27" t="n">
         <v>26.0</v>
@@ -1621,28 +1573,28 @@
         <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="J28" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="K28" t="n">
         <v>27.0</v>
@@ -1656,28 +1608,28 @@
         <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="K29" t="n">
         <v>28.0</v>
@@ -1691,28 +1643,28 @@
         <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E30" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
         <v>29.0</v>
@@ -1731,22 +1683,22 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
@@ -1754,22 +1706,22 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -1777,22 +1729,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1800,22 +1752,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -1823,22 +1775,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -1846,22 +1798,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
@@ -1869,22 +1821,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -1892,22 +1844,22 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -1915,22 +1867,22 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -1938,22 +1890,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -1961,22 +1913,22 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1984,22 +1936,22 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2007,22 +1959,22 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -2030,22 +1982,22 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -2053,22 +2005,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>17</v>
       </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16">
@@ -2076,22 +2028,22 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -2099,22 +2051,22 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -2122,22 +2074,22 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -2145,22 +2097,22 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -2168,22 +2120,22 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -2191,22 +2143,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -2214,22 +2166,22 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -2237,22 +2189,22 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -2260,22 +2212,22 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
@@ -2283,22 +2235,22 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26">
@@ -2306,22 +2258,22 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
@@ -2329,22 +2281,22 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2352,22 +2304,22 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -2375,22 +2327,22 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G29" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -2401,7 +2353,7 @@
         <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -2410,10 +2362,10 @@
         <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2429,128 +2381,128 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -2559,329 +2511,329 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
       <c r="G13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21">
@@ -2889,22 +2841,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -2912,160 +2864,160 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s">
         <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
@@ -3073,22 +3025,22 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
         <v>16</v>
       </c>
       <c r="F29" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
         <v>74</v>
-      </c>
-      <c r="G29" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -3096,22 +3048,22 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="G30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3165,28 +3117,28 @@
         <v>147</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>109</v>
-      </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="J2" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="K2" t="n">
         <v>1.0</v>
@@ -3200,28 +3152,28 @@
         <v>148</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="K3" t="n">
         <v>2.0</v>
@@ -3235,28 +3187,28 @@
         <v>149</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="K4" t="n">
         <v>3.0</v>
@@ -3270,28 +3222,28 @@
         <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="K5" t="n">
         <v>4.0</v>
@@ -3305,28 +3257,28 @@
         <v>151</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="K6" t="n">
         <v>5.0</v>
@@ -3340,28 +3292,28 @@
         <v>152</v>
       </c>
       <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I7" t="s">
         <v>10</v>
       </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>12</v>
-      </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="K7" t="n">
         <v>6.0</v>
@@ -3375,28 +3327,28 @@
         <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
         <v>7.0</v>
@@ -3410,28 +3362,28 @@
         <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
       <c r="J9" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
         <v>8.0</v>
@@ -3445,28 +3397,28 @@
         <v>155</v>
       </c>
       <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
         <v>11</v>
       </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" t="s">
-        <v>16</v>
-      </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="K10" t="n">
         <v>9.0</v>
@@ -3480,28 +3432,28 @@
         <v>156</v>
       </c>
       <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
         <v>12</v>
       </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>20</v>
-      </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
         <v>10.0</v>
@@ -3515,28 +3467,28 @@
         <v>157</v>
       </c>
       <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="I12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" t="s">
-        <v>93</v>
-      </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
         <v>11.0</v>
@@ -3550,28 +3502,28 @@
         <v>158</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="K13" t="n">
         <v>12.0</v>
@@ -3585,28 +3537,28 @@
         <v>159</v>
       </c>
       <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
         <v>18</v>
       </c>
-      <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" t="s">
-        <v>17</v>
-      </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="K14" t="n">
         <v>13.0</v>
@@ -3620,28 +3572,28 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I15" t="s">
         <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="K15" t="n">
         <v>14.0</v>
@@ -3655,28 +3607,28 @@
         <v>161</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
         <v>12</v>
       </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" t="s">
-        <v>16</v>
-      </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="K16" t="n">
         <v>15.0</v>
@@ -3690,28 +3642,28 @@
         <v>162</v>
       </c>
       <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>116</v>
       </c>
       <c r="K17" t="n">
         <v>16.0</v>
@@ -3725,28 +3677,28 @@
         <v>163</v>
       </c>
       <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
         <v>18</v>
       </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
         <v>12</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="s">
-        <v>21</v>
-      </c>
       <c r="H18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="J18" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
         <v>17.0</v>
@@ -3760,28 +3712,28 @@
         <v>164</v>
       </c>
       <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
       <c r="H19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K19" t="n">
         <v>18.0</v>
@@ -3795,28 +3747,28 @@
         <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
         <v>15</v>
       </c>
-      <c r="H20" t="s">
-        <v>19</v>
-      </c>
       <c r="I20" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K20" t="n">
         <v>19.0</v>
@@ -3830,28 +3782,28 @@
         <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
         <v>20.0</v>
@@ -3865,28 +3817,28 @@
         <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
         <v>16</v>
-      </c>
-      <c r="H22" t="s">
-        <v>21</v>
       </c>
       <c r="I22" t="s">
         <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="K22" t="n">
         <v>21.0</v>
@@ -3900,28 +3852,28 @@
         <v>168</v>
       </c>
       <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" t="s">
         <v>17</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
         <v>11</v>
       </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K23" t="n">
         <v>22.0</v>
@@ -3935,28 +3887,28 @@
         <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
         <v>12</v>
       </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s">
-        <v>19</v>
-      </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K24" t="n">
         <v>23.0</v>
@@ -3970,28 +3922,28 @@
         <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" t="s">
         <v>10</v>
       </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>175</v>
-      </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K25" t="n">
         <v>24.0</v>
@@ -4005,28 +3957,28 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" t="s">
         <v>13</v>
       </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K26" t="n">
         <v>25.0</v>
@@ -4040,28 +3992,28 @@
         <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
         <v>12</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K27" t="n">
         <v>26.0</v>
@@ -4075,28 +4027,28 @@
         <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I28" t="s">
-        <v>180</v>
+        <v>68</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="K28" t="n">
         <v>27.0</v>
@@ -4110,28 +4062,28 @@
         <v>174</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" t="s">
         <v>10</v>
       </c>
-      <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" t="s">
-        <v>100</v>
-      </c>
       <c r="J29" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="K29" t="n">
         <v>28.0</v>
@@ -4150,22 +4102,22 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" t="s">
         <v>181</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>182</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>183</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>184</v>
-      </c>
-      <c r="F1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="2">
@@ -4173,22 +4125,22 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -4196,22 +4148,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -4219,22 +4171,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -4242,22 +4194,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -4265,22 +4217,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -4288,22 +4240,22 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>188</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -4311,22 +4263,22 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -4334,22 +4286,22 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -4357,22 +4309,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
       <c r="G10" t="s">
-        <v>122</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -4380,22 +4332,22 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -4403,22 +4355,22 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -4426,22 +4378,22 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -4449,22 +4401,22 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -4472,22 +4424,22 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -4495,22 +4447,22 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -4518,22 +4470,22 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -4541,22 +4493,22 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -4564,22 +4516,22 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
         <v>32</v>
-      </c>
-      <c r="G19" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="20">
@@ -4587,22 +4539,22 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -4610,22 +4562,22 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -4633,22 +4585,22 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -4656,22 +4608,22 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -4679,22 +4631,22 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C24" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -4702,22 +4654,22 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -4725,22 +4677,22 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -4748,22 +4700,22 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -4771,22 +4723,22 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
@@ -4794,22 +4746,22 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>192</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -4825,298 +4777,298 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" t="s">
-        <v>79</v>
-      </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>198</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
       <c r="G10" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
         <v>20</v>
       </c>
-      <c r="B13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
       <c r="G13" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
@@ -5124,272 +5076,272 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G14" t="s">
-        <v>200</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
         <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>191</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>201</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C20" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
         <v>19</v>
       </c>
-      <c r="E21" t="s">
-        <v>31</v>
-      </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
         <v>84</v>
@@ -5397,94 +5349,94 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
         <v>17</v>
       </c>
-      <c r="B27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" t="s">
-        <v>14</v>
-      </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C28" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" t="s">
         <v>20</v>
       </c>
-      <c r="F29" t="s">
-        <v>84</v>
-      </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
